--- a/regressoes/cdx_us_hy/excel/out/US/Credit/HY/t_0/specs_fixed.xlsx
+++ b/regressoes/cdx_us_hy/excel/out/US/Credit/HY/t_0/specs_fixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\assistente_pesquisa\pietcon.github.io\regressoes\cdx_us_hy\excel\out\US\Credit\HY\t_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E572578-547B-4CFD-A745-7E18076AB33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB04D38-0512-4EF2-A2F3-FB8653904549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="22">
   <si>
     <t>jpm_vol</t>
   </si>
@@ -44,13 +44,7 @@
     <t>vix</t>
   </si>
   <si>
-    <t>10y_nom_dif_avg</t>
-  </si>
-  <si>
     <t>move</t>
-  </si>
-  <si>
-    <t>10y_nom</t>
   </si>
   <si>
     <t>CDX_US_HY_spread</t>
@@ -492,52 +486,52 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -545,13 +539,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
@@ -563,34 +557,31 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -642,19 +633,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
         <v>0</v>
@@ -715,7 +703,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>2</v>
@@ -726,10 +714,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
